--- a/output/pdf_financials_xlsx/SMAR.P.xlsx
+++ b/output/pdf_financials_xlsx/SMAR.P.xlsx
@@ -3681,28 +3681,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.044968</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.044968</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.044968</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.044968</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.044968</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.073973</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.073973</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.073973</v>
       </c>
     </row>
     <row r="93">
@@ -5499,7 +5499,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -5951,7 +5955,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -6134,7 +6142,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SMAR.P.xlsx
+++ b/output/pdf_financials_xlsx/SMAR.P.xlsx
@@ -724,28 +724,28 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.034587</v>
+        <v>0.087936</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.015748</v>
+        <v>0.024745</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.020751</v>
+        <v>0.07464800000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.031556</v>
+        <v>0.367212</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.017208</v>
+        <v>0.230519</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.02011</v>
+        <v>0.102868</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.015896</v>
+        <v>0.042514</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.016089</v>
+        <v>0.02899</v>
       </c>
     </row>
     <row r="11">
@@ -758,28 +758,28 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.034587</v>
+        <v>-0.087936</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.015748</v>
+        <v>-0.024745</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.020751</v>
+        <v>-0.07464800000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.031556</v>
+        <v>-0.367212</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.017208</v>
+        <v>-0.230519</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.02011</v>
+        <v>-0.102868</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.015896</v>
+        <v>-0.042514</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.016089</v>
+        <v>-0.02899</v>
       </c>
     </row>
     <row r="12">
@@ -795,10 +795,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004537</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003596</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -807,13 +807,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.005823</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.014026</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008843999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1357,10 +1357,10 @@
         <v>-0.087936</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.020208</v>
+        <v>-0.024745</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.071052</v>
+        <v>-0.07464800000000001</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.367212</v>
@@ -1369,13 +1369,13 @@
         <v>-0.480519</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.057955</v>
+        <v>0.052132</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.066512</v>
+        <v>0.052486</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.020146</v>
+        <v>-0.02899</v>
       </c>
     </row>
     <row r="28">
@@ -1425,10 +1425,10 @@
         <v>-0.087936</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.020208</v>
+        <v>-0.024745</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.071052</v>
+        <v>-0.07464800000000001</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.367212</v>
@@ -1437,13 +1437,13 @@
         <v>-0.480519</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.057955</v>
+        <v>0.052132</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.066512</v>
+        <v>0.052486</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.020146</v>
+        <v>-0.02899</v>
       </c>
     </row>
     <row r="30">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">

--- a/output/pdf_financials_xlsx/SMAR.P.xlsx
+++ b/output/pdf_financials_xlsx/SMAR.P.xlsx
@@ -6510,7 +6510,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
